--- a/output/20260630_fix_owner_new_import/membership_import_representative_28_examples_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/membership_import_representative_28_examples_20260630.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="T5" s="0" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       <c r="S14" s="0" t="n"/>
       <c r="T14" s="0" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="T30" s="0" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>

--- a/output/20260630_fix_owner_new_import/membership_import_representative_28_examples_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/membership_import_representative_28_examples_20260630.xlsx
@@ -148,8 +148,8 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="29.29" customWidth="1" style="19" min="1" max="1"/>
@@ -449,106 +449,111 @@
     <col width="19.29" customWidth="1" style="19" min="18" max="18"/>
     <col width="18.86" customWidth="1" style="19" min="19" max="19"/>
     <col width="21.86" customWidth="1" style="19" min="20" max="20"/>
-    <col width="8.710000000000001" customWidth="1" style="19" min="21" max="26"/>
+    <col width="12" customWidth="1" style="19" min="21" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>contract_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>client_fio</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>contract_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>card</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>duration_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>create_date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>payment_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>activation_date</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>freeze</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>guests</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>visits_left</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>amount_of_payments</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>payment_left</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>type_of_payment</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>manager</t>
         </is>
@@ -557,1094 +562,1100 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Тег</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>Внутренний номер абонемента</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Внутренний номер клиента</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Телефон клиента</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>ФИО клиента  *</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Название абонемента *</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Номер карты</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Продолжительность</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Тип продолжительности</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Дата  добавления *</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Дата оплаты *</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Дата активации </t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Дата окончания</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Осталось дней для заморозки</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>Осталось гостевых визитов</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>Осталось посещений *</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>Стоимость *</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Оплачено *</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>Осталось оплатить *</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>Тип оплаты</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="U2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Менеджер </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="0" t="n"/>
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>00000118260</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>000060002</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5437777</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Кудряшов Александр Васильевич</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>115000247314</t>
         </is>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="H3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="J3" s="21" t="n">
         <v>45293</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="K3" s="21" t="n">
         <v>45293</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="L3" s="21" t="n">
         <v>45293</v>
       </c>
-      <c r="L3" s="20" t="n">
+      <c r="M3" s="21" t="n">
         <v>45749</v>
-      </c>
-      <c r="M3" s="21" t="n"/>
-      <c r="P3" s="22" t="n">
-        <v>11990</v>
       </c>
       <c r="Q3" s="22" t="n">
         <v>11990</v>
       </c>
       <c r="R3" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="0" t="inlineStr">
+        <v>11990</v>
+      </c>
+      <c r="S3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T3" s="0" t="inlineStr">
+      <c r="U3" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" s="0" t="n"/>
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>00000118259</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>000012232</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5451323</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Полянская Жанна Михайловна</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>115000247819</t>
         </is>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="H4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="J4" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="K4" s="21" t="n">
         <v>45292</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="L4" s="21" t="n">
         <v>45292</v>
       </c>
-      <c r="L4" s="20" t="n">
+      <c r="M4" s="21" t="n">
         <v>45748</v>
-      </c>
-      <c r="M4" s="21" t="n"/>
-      <c r="P4" s="22" t="n">
-        <v>11990</v>
       </c>
       <c r="Q4" s="22" t="n">
         <v>11990</v>
       </c>
       <c r="R4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="0" t="inlineStr">
+        <v>11990</v>
+      </c>
+      <c r="S4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T4" s="0" t="inlineStr">
+      <c r="U4" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" s="0" t="n"/>
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>00000130520</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>000038077</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 6681017</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Иванова Екатерина Алексеевна</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12+2 месяца в подарок</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>115000109186</t>
         </is>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="H5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I5" s="20" t="n">
+      <c r="J5" s="21" t="n">
         <v>44489</v>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="K5" s="21" t="n">
         <v>45666</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="L5" s="21" t="n">
         <v>45666</v>
       </c>
-      <c r="L5" s="20" t="n">
+      <c r="M5" s="21" t="n">
         <v>45936</v>
-      </c>
-      <c r="M5" s="21" t="n"/>
-      <c r="P5" s="22" t="n">
-        <v>13990</v>
       </c>
       <c r="Q5" s="22" t="n">
         <v>13990</v>
       </c>
       <c r="R5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="0" t="inlineStr">
+        <v>13990</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T5" s="0" t="inlineStr">
+      <c r="U5" s="0" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>00000130311</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>000061275</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5402000</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Сергеева Ирина Борисовна</t>
         </is>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>8411111113190</t>
         </is>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="H6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="0" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="J6" s="21" t="n">
         <v>45252</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="K6" s="21" t="n">
         <v>45660</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="L6" s="21" t="n">
         <v>45679</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="M6" s="21" t="n">
         <v>46133</v>
-      </c>
-      <c r="M6" s="21" t="n"/>
-      <c r="P6" s="22" t="n">
-        <v>14990</v>
       </c>
       <c r="Q6" s="22" t="n">
         <v>14990</v>
       </c>
       <c r="R6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="0" t="inlineStr">
+        <v>14990</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="0" t="inlineStr">
         <is>
           <t>сбп</t>
         </is>
       </c>
-      <c r="T6" s="0" t="inlineStr">
+      <c r="U6" s="0" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" s="0" t="n"/>
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>00000062156</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>000020780</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5252014</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Якушенков Александр Сергеевич</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>115000265233</t>
         </is>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="0" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="J7" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="K7" s="21" t="n">
         <v>43480</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="L7" s="21" t="n">
         <v>43480</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="M7" s="21" t="n">
         <v>44383</v>
-      </c>
-      <c r="M7" s="21" t="n"/>
-      <c r="P7" s="22" t="n">
-        <v>6499</v>
       </c>
       <c r="Q7" s="22" t="n">
         <v>6499</v>
       </c>
       <c r="R7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="0" t="inlineStr">
+        <v>6499</v>
+      </c>
+      <c r="S7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="0" t="inlineStr">
         <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="T7" s="0" t="inlineStr">
+      <c r="U7" s="0" t="inlineStr">
         <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" s="0" t="n"/>
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>00000074249</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>000025519</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>+7 (921) 8000849</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Койбин Игорь Анатольевич</t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ САЙТ</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>115000205130</t>
         </is>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="J8" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J8" s="20" t="n">
+      <c r="K8" s="21" t="n">
         <v>44113</v>
       </c>
-      <c r="K8" s="20" t="n">
+      <c r="L8" s="21" t="n">
         <v>44113</v>
       </c>
-      <c r="L8" s="20" t="n">
+      <c r="M8" s="21" t="n">
         <v>44120</v>
-      </c>
-      <c r="M8" s="21" t="n"/>
-      <c r="P8" s="22" t="n">
-        <v>7</v>
       </c>
       <c r="Q8" s="22" t="n">
         <v>7</v>
       </c>
       <c r="R8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="0" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="0" t="inlineStr">
         <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="T8" s="0" t="inlineStr">
+      <c r="U8" s="0" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" s="0" t="n"/>
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>00000145604</t>
         </is>
       </c>
-      <c r="B9" s="0" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>000027130</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 4050018</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Мамай Анастасия Витальевна</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ</t>
         </is>
       </c>
-      <c r="F9" s="0" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>115000151321</t>
         </is>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="0" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="J9" s="21" t="n">
         <v>45213</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="K9" s="21" t="n">
         <v>46039</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="L9" s="21" t="n">
         <v>46039</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="M9" s="21" t="n">
         <v>46403</v>
-      </c>
-      <c r="M9" s="21" t="n"/>
-      <c r="P9" s="22" t="n">
-        <v>11990</v>
       </c>
       <c r="Q9" s="22" t="n">
         <v>11990</v>
       </c>
       <c r="R9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="0" t="inlineStr">
+        <v>11990</v>
+      </c>
+      <c r="S9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="0" t="inlineStr">
         <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="T9" s="0" t="inlineStr">
+      <c r="U9" s="0" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" s="0" t="n"/>
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>00000043166</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>000013446</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 6687253, +7 (921) 8042001</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Пашук Алена Евгеньевна</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F10" s="0" t="n"/>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="0" t="n"/>
+      <c r="H10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" s="0" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="J10" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="K10" s="21" t="n">
         <v>43582</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="L10" s="21" t="n">
         <v>43582</v>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="M10" s="21" t="n">
         <v>44029</v>
       </c>
-      <c r="M10" s="21" t="n">
+      <c r="N10" t="n">
         <v>180</v>
-      </c>
-      <c r="P10" s="22" t="n">
-        <v>6599</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>6599</v>
       </c>
       <c r="R10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="0" t="inlineStr">
+        <v>6599</v>
+      </c>
+      <c r="S10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T10" s="0" t="inlineStr">
+      <c r="U10" s="0" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>00000145377</t>
         </is>
       </c>
-      <c r="B11" s="0" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>000026744</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 4346761</t>
         </is>
       </c>
-      <c r="D11" s="0" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Савельева Екатерина Владимировна</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>115000277793</t>
         </is>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="H11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="0" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="J11" s="21" t="n">
         <v>43626</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="K11" s="21" t="n">
         <v>46035</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="L11" s="21" t="n">
         <v>46035</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="M11" s="21" t="n">
         <v>46399</v>
       </c>
-      <c r="M11" s="21" t="n"/>
-      <c r="P11" s="22" t="n">
+      <c r="Q11" s="22" t="n">
         <v>14990</v>
-      </c>
-      <c r="Q11" s="22" t="n">
-        <v>7495</v>
       </c>
       <c r="R11" s="22" t="n">
         <v>7495</v>
       </c>
-      <c r="S11" s="0" t="inlineStr">
+      <c r="S11" s="22" t="n">
+        <v>7495</v>
+      </c>
+      <c r="T11" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T11" s="0" t="inlineStr">
+      <c r="U11" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>00000150216</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>000061678</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 6616085</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Яршина Ангелина Витальевна</t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев (рассрочка)</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>115000278806</t>
         </is>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="H12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="J12" s="21" t="n">
         <v>45286</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="K12" s="21" t="n">
         <v>46155</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="L12" s="21" t="n">
         <v>46155</v>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="M12" s="21" t="n">
         <v>46611</v>
       </c>
-      <c r="M12" s="21" t="n"/>
-      <c r="P12" s="22" t="n">
+      <c r="Q12" s="22" t="n">
         <v>11990</v>
-      </c>
-      <c r="Q12" s="22" t="n">
-        <v>5995</v>
       </c>
       <c r="R12" s="22" t="n">
         <v>5995</v>
       </c>
-      <c r="S12" s="0" t="inlineStr">
+      <c r="S12" s="22" t="n">
+        <v>5995</v>
+      </c>
+      <c r="T12" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T12" s="0" t="inlineStr">
+      <c r="U12" s="0" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
+      <c r="A13" s="0" t="n"/>
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>00000130403</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>000066861</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>+7 (921) 4581114</t>
         </is>
       </c>
-      <c r="D13" s="0" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Лепегова Илона Викторовна</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F13" s="0" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>8111111113946</t>
         </is>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="H13" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="0" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="J13" s="21" t="n">
         <v>45664</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="K13" s="21" t="n">
         <v>45664</v>
       </c>
-      <c r="K13" s="20" t="n">
+      <c r="L13" s="21" t="n">
         <v>45666</v>
       </c>
-      <c r="L13" s="20" t="n">
+      <c r="M13" s="21" t="n">
         <v>46120</v>
-      </c>
-      <c r="M13" s="21" t="n"/>
-      <c r="P13" s="22" t="n">
-        <v>14990</v>
       </c>
       <c r="Q13" s="22" t="n">
         <v>14990</v>
       </c>
       <c r="R13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="0" t="inlineStr">
+        <v>14990</v>
+      </c>
+      <c r="S13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T13" s="0" t="inlineStr">
+      <c r="U13" s="0" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>00000046946</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>000026915</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5370300</t>
         </is>
       </c>
-      <c r="D14" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Демидова Надежда Викторовна</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F14" s="0" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>115000115774</t>
         </is>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="H14" s="0" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="J14" s="21" t="n">
         <v>43616</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="K14" s="21" t="n">
         <v>43616</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="L14" s="21" t="n">
         <v>43616</v>
       </c>
-      <c r="L14" s="20" t="n">
+      <c r="M14" s="21" t="n">
         <v>44187</v>
       </c>
-      <c r="M14" s="21" t="n"/>
-      <c r="P14" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="0" t="n"/>
-      <c r="T14" s="0" t="inlineStr">
+      <c r="S14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="0" t="n"/>
+      <c r="U14" s="0" t="inlineStr">
         <is>
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" s="0" t="n"/>
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>00000031506</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>000000014</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>+7 (996) 9638517</t>
         </is>
       </c>
-      <c r="D15" s="0" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Абашкина Анна Евгеньевна</t>
         </is>
       </c>
-      <c r="E15" s="0" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F15" s="0" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>1150003139418</t>
         </is>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="H15" t="n">
         <v>18</v>
       </c>
-      <c r="H15" s="0" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="J15" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J15" s="20" t="n">
+      <c r="K15" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="L15" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="L15" s="20" t="n">
+      <c r="M15" s="21" t="n">
         <v>43639</v>
       </c>
-      <c r="M15" s="21" t="n"/>
-      <c r="P15" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="0" t="n"/>
-      <c r="T15" s="0" t="inlineStr">
+      <c r="S15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="0" t="n"/>
+      <c r="U15" s="0" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>00000043326</t>
         </is>
       </c>
-      <c r="B16" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>000010687</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>+7 (981) 4033028</t>
         </is>
       </c>
-      <c r="D16" s="0" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Максимова Елена Владимировна</t>
         </is>
       </c>
-      <c r="E16" s="0" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ ДРУГ</t>
         </is>
       </c>
-      <c r="F16" s="0" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>1150004046630</t>
         </is>
       </c>
-      <c r="G16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="J16" s="21" t="n">
         <v>43591</v>
       </c>
-      <c r="J16" s="20" t="n">
+      <c r="K16" s="21" t="n">
         <v>43591</v>
       </c>
-      <c r="K16" s="20" t="n">
+      <c r="L16" s="21" t="n">
         <v>43591</v>
       </c>
-      <c r="L16" s="20" t="n">
+      <c r="M16" s="21" t="n">
         <v>43598</v>
       </c>
-      <c r="M16" s="21" t="n"/>
-      <c r="P16" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="0" t="n"/>
-      <c r="T16" s="0" t="inlineStr">
+      <c r="S16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="0" t="n"/>
+      <c r="U16" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
@@ -1653,134 +1664,138 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
           <t>00000149560</t>
         </is>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>000073618</t>
         </is>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>+7 (963) 7496314</t>
         </is>
       </c>
-      <c r="D17" s="0" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Сарин Павел Сергеевич</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>Абонемент 10 ДНЕЙ</t>
         </is>
       </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>1111111143964</t>
         </is>
       </c>
-      <c r="G17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I17" s="20" t="n">
+      <c r="J17" s="21" t="n">
         <v>46135</v>
       </c>
-      <c r="J17" s="20" t="n">
+      <c r="K17" s="21" t="n">
         <v>46135</v>
       </c>
-      <c r="K17" s="20" t="n">
+      <c r="L17" s="21" t="n">
         <v>46135</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="M17" s="21" t="n">
         <v>46145</v>
       </c>
-      <c r="M17" s="21" t="n"/>
-      <c r="P17" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="0" t="n"/>
-      <c r="T17" s="0" t="inlineStr">
+      <c r="S17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="0" t="n"/>
+      <c r="U17" s="0" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" s="0" t="n"/>
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>00000041546</t>
         </is>
       </c>
-      <c r="B18" s="0" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>000023699</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 0528656</t>
         </is>
       </c>
-      <c r="D18" s="0" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Путкова Елизавета Алексеевна</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ САЙТ</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>000040035581</t>
         </is>
       </c>
-      <c r="G18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I18" s="20" t="n">
+      <c r="J18" s="21" t="n">
         <v>43523</v>
       </c>
-      <c r="J18" s="20" t="n">
+      <c r="K18" s="21" t="n">
         <v>43523</v>
       </c>
-      <c r="K18" s="20" t="n">
+      <c r="L18" s="21" t="n">
         <v>43523</v>
       </c>
-      <c r="L18" s="20" t="n">
+      <c r="M18" s="21" t="n">
         <v>43530</v>
       </c>
-      <c r="M18" s="21" t="n"/>
-      <c r="P18" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="0" t="n"/>
-      <c r="T18" s="0" t="inlineStr">
+      <c r="S18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="0" t="n"/>
+      <c r="U18" s="0" t="inlineStr">
         <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
@@ -1789,412 +1804,417 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
           <t>00000098600</t>
         </is>
       </c>
-      <c r="B19" s="0" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>000044469</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>+7 (981) 4019377</t>
         </is>
       </c>
-      <c r="D19" s="0" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Кодиров Салимбек Хуршедович</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ ФИТНЕСА БЕСПЛАТНО</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>1329000081703</t>
         </is>
       </c>
-      <c r="G19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I19" s="20" t="n">
+      <c r="J19" s="21" t="n">
         <v>44254</v>
       </c>
-      <c r="J19" s="20" t="n">
+      <c r="K19" s="21" t="n">
         <v>44669</v>
       </c>
-      <c r="K19" s="20" t="n">
+      <c r="L19" s="21" t="n">
         <v>44669</v>
       </c>
-      <c r="L19" s="20" t="n">
+      <c r="M19" s="21" t="n">
         <v>44675</v>
       </c>
-      <c r="M19" s="21" t="n"/>
-      <c r="P19" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="0" t="n"/>
-      <c r="T19" s="0" t="inlineStr">
+      <c r="S19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="0" t="n"/>
+      <c r="U19" s="0" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="A20" s="0" t="n"/>
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>00000114628</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>000059966</t>
         </is>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>+7 (964) 3092913</t>
         </is>
       </c>
-      <c r="D20" s="0" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>Бессмертная Анна Сергеевна</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>Абонемент Неделя Фитнес</t>
         </is>
       </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>8211111115510</t>
         </is>
       </c>
-      <c r="G20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="J20" s="21" t="n">
         <v>45182</v>
       </c>
-      <c r="J20" s="20" t="n">
+      <c r="K20" s="21" t="n">
         <v>45182</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="L20" s="21" t="n">
         <v>45182</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="M20" s="21" t="n">
         <v>45188</v>
       </c>
-      <c r="M20" s="21" t="n"/>
-      <c r="P20" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="0" t="n"/>
-      <c r="T20" s="0" t="inlineStr">
+      <c r="S20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="0" t="n"/>
+      <c r="U20" s="0" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" s="0" t="n"/>
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>00000100577</t>
         </is>
       </c>
-      <c r="B21" s="0" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>000024568</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 4372967</t>
         </is>
       </c>
-      <c r="D21" s="0" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>Чуркина Виктория Сергеевна</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>СУБАРЕНДА безлимит</t>
         </is>
       </c>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>000040084374</t>
         </is>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="0" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="J21" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J21" s="20" t="n">
+      <c r="K21" s="21" t="n">
         <v>44740</v>
       </c>
-      <c r="K21" s="20" t="n">
+      <c r="L21" s="21" t="n">
         <v>44743</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="M21" s="21" t="n">
         <v>44773</v>
       </c>
-      <c r="M21" s="21" t="n"/>
-      <c r="P21" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="0" t="n"/>
-      <c r="T21" s="0" t="inlineStr">
+      <c r="S21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="0" t="n"/>
+      <c r="U21" s="0" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="A22" s="0" t="n"/>
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>00000055624</t>
         </is>
       </c>
-      <c r="B22" s="0" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>000023705</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>+7 (921) 7003199</t>
         </is>
       </c>
-      <c r="D22" s="0" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>Детчуева Елена Павловна</t>
         </is>
       </c>
-      <c r="E22" s="0" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F22" s="0" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>8811111112788</t>
         </is>
       </c>
-      <c r="G22" s="0" t="n">
+      <c r="H22" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="0" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I22" s="20" t="n">
+      <c r="J22" s="21" t="n">
         <v>43524</v>
       </c>
-      <c r="J22" s="20" t="n">
+      <c r="K22" s="21" t="n">
         <v>43524</v>
       </c>
-      <c r="K22" s="20" t="n">
+      <c r="L22" s="21" t="n">
         <v>43524</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="M22" s="21" t="n">
         <v>44029</v>
       </c>
-      <c r="M22" s="21" t="n">
+      <c r="N22" t="n">
         <v>180</v>
       </c>
-      <c r="P22" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="0" t="n"/>
-      <c r="T22" s="0" t="inlineStr">
+      <c r="S22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="0" t="n"/>
+      <c r="U22" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="19">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" s="0" t="n"/>
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>00000107036</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>000056054</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>+7 (960) 2139886</t>
         </is>
       </c>
-      <c r="D23" s="0" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>Боярова Галина Федоровна</t>
         </is>
       </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>Абонемент Неделя сайт 2023</t>
         </is>
       </c>
-      <c r="F23" s="0" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>1111111123805</t>
         </is>
       </c>
-      <c r="G23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I23" s="20" t="n">
+      <c r="J23" s="21" t="n">
         <v>44948</v>
       </c>
-      <c r="J23" s="20" t="n">
+      <c r="K23" s="21" t="n">
         <v>44948</v>
       </c>
-      <c r="K23" s="20" t="n">
+      <c r="L23" s="21" t="n">
         <v>44950</v>
       </c>
-      <c r="L23" s="20" t="n">
+      <c r="M23" s="21" t="n">
         <v>44986</v>
       </c>
-      <c r="M23" s="21" t="n"/>
-      <c r="P23" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="0" t="n"/>
-      <c r="T23" s="0" t="inlineStr">
+      <c r="S23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="0" t="n"/>
+      <c r="U23" s="0" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="19">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="A24" s="0" t="n"/>
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>00000139318</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>000069754</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5287037</t>
         </is>
       </c>
-      <c r="D24" s="0" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>Ермакова Елена Александровна</t>
         </is>
       </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F24" s="0" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>115000230712</t>
         </is>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="H24" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="0" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I24" s="20" t="n">
+      <c r="J24" s="21" t="n">
         <v>45892</v>
       </c>
-      <c r="J24" s="20" t="n">
+      <c r="K24" s="21" t="n">
         <v>45892</v>
       </c>
-      <c r="K24" s="20" t="n">
+      <c r="L24" s="21" t="n">
         <v>45892</v>
       </c>
-      <c r="L24" s="20" t="n">
+      <c r="M24" s="21" t="n">
         <v>46316</v>
       </c>
-      <c r="M24" s="21" t="n"/>
-      <c r="P24" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="0" t="inlineStr">
+      <c r="S24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T24" s="0" t="inlineStr">
+      <c r="U24" s="0" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
@@ -2203,216 +2223,220 @@
     <row r="25" ht="15.75" customHeight="1" s="19">
       <c r="A25" s="0" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
           <t>00000090734</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>000016248</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>+7 (905) 2995684</t>
         </is>
       </c>
-      <c r="D25" s="0" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>Сидоров Сергей Николаевич (Тренер)</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>СУБАРЕНДА безлимит</t>
         </is>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>2407201500540</t>
         </is>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="0" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I25" s="20" t="n">
+      <c r="J25" s="21" t="n">
         <v>43998</v>
       </c>
-      <c r="J25" s="20" t="n">
+      <c r="K25" s="21" t="n">
         <v>44463</v>
       </c>
-      <c r="K25" s="20" t="n">
+      <c r="L25" s="21" t="n">
         <v>44470</v>
       </c>
-      <c r="L25" s="20" t="n">
+      <c r="M25" s="21" t="n">
         <v>44500</v>
-      </c>
-      <c r="M25" s="21" t="n"/>
-      <c r="P25" s="22" t="n">
-        <v>25500</v>
       </c>
       <c r="Q25" s="22" t="n">
         <v>25500</v>
       </c>
       <c r="R25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="0" t="inlineStr">
+        <v>25500</v>
+      </c>
+      <c r="S25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T25" s="0" t="inlineStr">
+      <c r="U25" s="0" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="19">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" s="0" t="n"/>
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>00000149696</t>
         </is>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>000023964</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 4172746, +7 (981) 4039028</t>
         </is>
       </c>
-      <c r="D26" s="0" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>Ивашко Анна Владимировна (Тренер)</t>
         </is>
       </c>
-      <c r="E26" s="0" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>СУБАРЕНДА 15 посещений</t>
         </is>
       </c>
-      <c r="F26" s="0" t="n"/>
-      <c r="G26" s="0" t="n">
+      <c r="G26" s="0" t="n"/>
+      <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I26" s="20" t="n">
+      <c r="J26" s="21" t="n">
         <v>43553</v>
       </c>
-      <c r="J26" s="20" t="n">
+      <c r="K26" s="21" t="n">
         <v>46140</v>
       </c>
-      <c r="K26" s="20" t="n">
+      <c r="L26" s="21" t="n">
         <v>46141</v>
       </c>
-      <c r="L26" s="20" t="n">
+      <c r="M26" s="21" t="n">
         <v>46170</v>
       </c>
-      <c r="M26" s="21" t="n"/>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>2</v>
-      </c>
-      <c r="P26" s="22" t="n">
-        <v>22000</v>
       </c>
       <c r="Q26" s="22" t="n">
         <v>22000</v>
       </c>
       <c r="R26" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="0" t="inlineStr">
+        <v>22000</v>
+      </c>
+      <c r="S26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T26" s="0" t="inlineStr">
+      <c r="U26" s="0" t="inlineStr">
         <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="19">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A27" s="0" t="n"/>
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>00000149630</t>
         </is>
       </c>
-      <c r="B27" s="0" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>000028600</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>+7 (911) 4372448</t>
         </is>
       </c>
-      <c r="D27" s="0" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>Савельева Александра Александровна (Тренер)</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>СУБАРЕНДА 12 посещений</t>
         </is>
       </c>
-      <c r="F27" s="0" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>000040062204</t>
         </is>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I27" s="20" t="n">
+      <c r="J27" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J27" s="20" t="n">
+      <c r="K27" s="21" t="n">
         <v>46139</v>
       </c>
-      <c r="K27" s="20" t="n">
+      <c r="L27" s="21" t="n">
         <v>46139</v>
       </c>
-      <c r="L27" s="20" t="n">
+      <c r="M27" s="21" t="n">
         <v>46168</v>
       </c>
-      <c r="M27" s="21" t="n"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="22" t="n">
-        <v>20000</v>
+      <c r="P27" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" s="22" t="n">
         <v>20000</v>
       </c>
       <c r="R27" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="0" t="inlineStr">
+        <v>20000</v>
+      </c>
+      <c r="S27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T27" s="0" t="inlineStr">
+      <c r="U27" s="0" t="inlineStr">
         <is>
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
@@ -2421,217 +2445,221 @@
     <row r="28" ht="15.75" customHeight="1" s="19">
       <c r="A28" s="0" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
           <t>00000090698</t>
         </is>
       </c>
-      <c r="B28" s="0" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>000004751</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>+7 (921) 5245848</t>
         </is>
       </c>
-      <c r="D28" s="0" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>Дергачев Дмитрий Игоревич ( Тренер )</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>СУБАРЕНДА 15 посещений</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>1150000655058</t>
         </is>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="H28" t="n">
         <v>30</v>
       </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="J28" s="21" t="n">
         <v>44006</v>
       </c>
-      <c r="J28" s="20" t="n">
+      <c r="K28" s="21" t="n">
         <v>44462</v>
       </c>
-      <c r="K28" s="20" t="n">
+      <c r="L28" s="21" t="n">
         <v>44470</v>
       </c>
-      <c r="L28" s="20" t="n">
+      <c r="M28" s="21" t="n">
         <v>44499</v>
       </c>
-      <c r="M28" s="21" t="n"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="22" t="n">
-        <v>15000</v>
+      <c r="P28" t="n">
+        <v>0</v>
       </c>
       <c r="Q28" s="22" t="n">
         <v>15000</v>
       </c>
       <c r="R28" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="0" t="inlineStr">
+        <v>15000</v>
+      </c>
+      <c r="S28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T28" s="0" t="inlineStr">
+      <c r="U28" s="0" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="19">
-      <c r="A29" s="0" t="inlineStr">
+      <c r="A29" s="0" t="n"/>
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>00000041909</t>
         </is>
       </c>
-      <c r="B29" s="0" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>000023002</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>+7 (981) 4057564, +7 (981) 4022510</t>
         </is>
       </c>
-      <c r="D29" s="0" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>Терновых Светлана Олеговна</t>
         </is>
       </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>Абонемент в солярий на 50 минут</t>
         </is>
       </c>
-      <c r="F29" s="0" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>115000185883</t>
         </is>
       </c>
-      <c r="G29" s="0" t="n">
+      <c r="H29" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="0" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I29" s="20" t="n">
+      <c r="J29" s="21" t="n">
         <v>43101</v>
       </c>
-      <c r="J29" s="20" t="n">
+      <c r="K29" s="21" t="n">
         <v>43516</v>
       </c>
-      <c r="K29" s="20" t="n">
+      <c r="L29" s="21" t="n">
         <v>43516</v>
       </c>
-      <c r="L29" s="20" t="n">
+      <c r="M29" s="21" t="n">
         <v>43575</v>
-      </c>
-      <c r="M29" s="21" t="n"/>
-      <c r="P29" s="22" t="n">
-        <v>499</v>
       </c>
       <c r="Q29" s="22" t="n">
         <v>499</v>
       </c>
       <c r="R29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="0" t="inlineStr">
+        <v>499</v>
+      </c>
+      <c r="S29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="0" t="inlineStr">
         <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="T29" s="0" t="inlineStr">
+      <c r="U29" s="0" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="19">
-      <c r="A30" s="0" t="inlineStr">
+      <c r="A30" s="0" t="n"/>
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>00000074295</t>
         </is>
       </c>
-      <c r="B30" s="0" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>000039694</t>
         </is>
       </c>
-      <c r="C30" s="0" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>+7 (953) 5339838</t>
         </is>
       </c>
-      <c r="D30" s="0" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>Толмачева Надежда Сергеевна</t>
         </is>
       </c>
-      <c r="E30" s="0" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ САЙТ</t>
         </is>
       </c>
-      <c r="F30" s="0" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>000040060835</t>
         </is>
       </c>
-      <c r="G30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="0" t="inlineStr">
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="I30" s="20" t="n">
+      <c r="J30" s="21" t="n">
         <v>44113</v>
       </c>
-      <c r="J30" s="20" t="n">
+      <c r="K30" s="21" t="n">
         <v>44113</v>
       </c>
-      <c r="K30" s="20" t="n">
+      <c r="L30" s="21" t="n">
         <v>44113</v>
       </c>
-      <c r="L30" s="20" t="n">
+      <c r="M30" s="21" t="n">
         <v>44121</v>
-      </c>
-      <c r="M30" s="21" t="n"/>
-      <c r="P30" s="22" t="n">
-        <v>7</v>
       </c>
       <c r="Q30" s="22" t="n">
         <v>7</v>
       </c>
       <c r="R30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="0" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="S30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="0" t="inlineStr">
         <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="T30" s="0" t="inlineStr">
+      <c r="U30" s="0" t="inlineStr">
         <is>
           <t>Фёдорова Милана Андреевна</t>
         </is>
